--- a/artfynd/A 28422-2026 artfynd.xlsx
+++ b/artfynd/A 28422-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647360</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135647337</v>
       </c>
       <c r="B4" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647339</v>
       </c>
       <c r="B5" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135647340</v>
       </c>
       <c r="B6" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135647341</v>
       </c>
       <c r="B7" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135647342</v>
       </c>
       <c r="B8" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135647345</v>
       </c>
       <c r="B9" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135647348</v>
       </c>
       <c r="B10" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135647350</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135647352</v>
       </c>
       <c r="B12" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135647354</v>
       </c>
       <c r="B13" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135647356</v>
       </c>
       <c r="B14" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135647361</v>
       </c>
       <c r="B15" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135647362</v>
       </c>
       <c r="B16" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 28422-2026 artfynd.xlsx
+++ b/artfynd/A 28422-2026 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>135647337</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647339</v>
       </c>
       <c r="B5" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135647340</v>
       </c>
       <c r="B6" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135647341</v>
       </c>
       <c r="B7" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135647342</v>
       </c>
       <c r="B8" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135647345</v>
       </c>
       <c r="B9" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135647348</v>
       </c>
       <c r="B10" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135647350</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135647352</v>
       </c>
       <c r="B12" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135647354</v>
       </c>
       <c r="B13" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135647356</v>
       </c>
       <c r="B14" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135647361</v>
       </c>
       <c r="B15" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135647362</v>
       </c>
       <c r="B16" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 28422-2026 artfynd.xlsx
+++ b/artfynd/A 28422-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647360</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135647338</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135647337</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647339</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135647340</v>
       </c>
       <c r="B6" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135647341</v>
       </c>
       <c r="B7" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135647342</v>
       </c>
       <c r="B8" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135647345</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135647348</v>
       </c>
       <c r="B10" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135647350</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135647352</v>
       </c>
       <c r="B12" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135647354</v>
       </c>
       <c r="B13" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135647356</v>
       </c>
       <c r="B14" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135647361</v>
       </c>
       <c r="B15" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135647362</v>
       </c>
       <c r="B16" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 28422-2026 artfynd.xlsx
+++ b/artfynd/A 28422-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647360</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135647337</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647339</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135647340</v>
       </c>
       <c r="B6" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135647341</v>
       </c>
       <c r="B7" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135647342</v>
       </c>
       <c r="B8" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135647345</v>
       </c>
       <c r="B9" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135647348</v>
       </c>
       <c r="B10" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135647350</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135647352</v>
       </c>
       <c r="B12" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135647354</v>
       </c>
       <c r="B13" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135647356</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135647361</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135647362</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 28422-2026 artfynd.xlsx
+++ b/artfynd/A 28422-2026 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>135647337</v>
       </c>
       <c r="B4" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647339</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135647340</v>
       </c>
       <c r="B6" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135647341</v>
       </c>
       <c r="B7" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135647342</v>
       </c>
       <c r="B8" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135647345</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135647348</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135647350</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135647352</v>
       </c>
       <c r="B12" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135647354</v>
       </c>
       <c r="B13" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135647356</v>
       </c>
       <c r="B14" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135647361</v>
       </c>
       <c r="B15" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135647362</v>
       </c>
       <c r="B16" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 28422-2026 artfynd.xlsx
+++ b/artfynd/A 28422-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647360</v>
       </c>
       <c r="B2" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135647338</v>
       </c>
       <c r="B3" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135647337</v>
       </c>
       <c r="B4" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647339</v>
       </c>
       <c r="B5" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135647340</v>
       </c>
       <c r="B6" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135647341</v>
       </c>
       <c r="B7" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135647342</v>
       </c>
       <c r="B8" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135647345</v>
       </c>
       <c r="B9" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135647348</v>
       </c>
       <c r="B10" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135647350</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135647352</v>
       </c>
       <c r="B12" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135647354</v>
       </c>
       <c r="B13" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135647356</v>
       </c>
       <c r="B14" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135647361</v>
       </c>
       <c r="B15" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135647362</v>
       </c>
       <c r="B16" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 28422-2026 artfynd.xlsx
+++ b/artfynd/A 28422-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135647360</v>
       </c>
       <c r="B2" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135647338</v>
       </c>
       <c r="B3" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135647337</v>
       </c>
       <c r="B4" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135647339</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1141,7 +1141,7 @@
         <v>135647340</v>
       </c>
       <c r="B6" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1253,7 +1253,7 @@
         <v>135647341</v>
       </c>
       <c r="B7" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>135647342</v>
       </c>
       <c r="B8" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1477,7 +1477,7 @@
         <v>135647345</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
         <v>135647348</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1701,7 +1701,7 @@
         <v>135647350</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>135647352</v>
       </c>
       <c r="B12" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>135647354</v>
       </c>
       <c r="B13" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
         <v>135647356</v>
       </c>
       <c r="B14" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>135647361</v>
       </c>
       <c r="B15" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>135647362</v>
       </c>
       <c r="B16" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
